--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,277 +656,284 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1038800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1123000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>933300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>876400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>783100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>866400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>698500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>659200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>576200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>591100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>496500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>445800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>381000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>340000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>298000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>308900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>302300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>303300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>238400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>219200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>214300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>189500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>157500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>141800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>128400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>125200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>82200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>69600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>576900</v>
+      </c>
+      <c r="E9" s="3">
         <v>540600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>580500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>478100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>451300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>430600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>447000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>413400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>349800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>345200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>349300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>284200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>263700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>214100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -972,53 +979,56 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>589100</v>
+      </c>
+      <c r="E10" s="3">
         <v>498200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>542500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>455200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>425100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>352600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>419400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>285100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>309400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>230900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>241800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>212400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>182100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>166900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,53 +1111,54 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>202600</v>
+      </c>
+      <c r="E12" s="3">
         <v>191600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>184900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>168100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>154600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>152600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>148200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>134300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>124200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>124800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>119800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>133000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>152300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>161800</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,145 +1299,151 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3">
-        <v>800</v>
-      </c>
       <c r="H14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-16900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-13200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-87600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>34900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-21200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-28000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-15000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-5600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>20700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>24300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>57200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>55200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>49400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>43700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>33700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>37900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E15" s="3">
         <v>78100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>80400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>73400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>72000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>70400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>61000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>79500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>52900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>48100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>61700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>64600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>68600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1018700</v>
+      </c>
+      <c r="E17" s="3">
         <v>950300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1005400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>869700</v>
       </c>
-      <c r="G17" s="3">
-        <v>819200</v>
-      </c>
       <c r="H17" s="3">
+        <v>818400</v>
+      </c>
+      <c r="I17" s="3">
         <v>791500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>870600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>831400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>731000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>731700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>762200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>703600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>687400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>656100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>699500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>585500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>586100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>528800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>499500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>404500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>333500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>423700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>216300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>190800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>102400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>209900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>157900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>115200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>110300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E18" s="3">
         <v>88400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>117600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>63700</v>
       </c>
-      <c r="G18" s="3">
-        <v>57300</v>
-      </c>
       <c r="H18" s="3">
+        <v>58100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-132900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-71900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-155600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-171100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-207000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-241500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-275100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-359500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-287500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-277200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-226500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-196200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-166100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-114300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-209400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-26800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-33300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>39400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-81500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-32700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-40700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1748,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-21600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-88200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-18400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-19500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-39600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>52500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-104500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>35500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>36000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>72700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>172100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-140400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-77800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>29500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E21" s="3">
         <v>188100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>216300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>157600</v>
       </c>
-      <c r="G21" s="3">
-        <v>147000</v>
-      </c>
       <c r="H21" s="3">
+        <v>147800</v>
+      </c>
+      <c r="I21" s="3">
         <v>78300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>153100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-74100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-103500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-105700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-229400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-301000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-230600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-187400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-41300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-147500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-295900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-118000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-282100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1920,16 +1960,16 @@
         <v>2700</v>
       </c>
       <c r="I22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J22" s="3">
         <v>1000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
       </c>
       <c r="L22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>900</v>
@@ -1938,14 +1978,14 @@
         <v>900</v>
       </c>
       <c r="O22" s="3">
+        <v>900</v>
+      </c>
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1991,168 +2031,174 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>169100</v>
+      </c>
+      <c r="E23" s="3">
         <v>107400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>133200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>83000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>71600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>82900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-98300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-133000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-167600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-170700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-207300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-206500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-324000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-251400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-204500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-54400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-159500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-306400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-125900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>34900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-85500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-30900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-30700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-36400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1447500</v>
+      </c>
+      <c r="E24" s="3">
         <v>4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2300</v>
       </c>
       <c r="G24" s="3">
         <v>2300</v>
       </c>
       <c r="H24" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="I24" s="3">
         <v>2500</v>
       </c>
       <c r="J24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
@@ -2170,13 +2216,16 @@
         <v>100</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1616600</v>
+      </c>
+      <c r="E26" s="3">
         <v>102900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>129600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>80700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>69200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>80400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-133900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-166900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-171800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-206000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-205700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-322400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-251300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-186400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-54700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-159700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-306600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-123400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>34800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-85600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-31000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1616600</v>
+      </c>
+      <c r="E27" s="3">
         <v>102900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>129600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>80700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>69200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>80400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-133900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-166900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-171800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-206000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-205700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-322400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-251300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-186400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-54700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-159700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-306600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-123400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-85600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E32" s="3">
         <v>21600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>88200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>18400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>19500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>39600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-52500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>104500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-35500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-36000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-72700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-172100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>140400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>77800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1616600</v>
+      </c>
+      <c r="E33" s="3">
         <v>102900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>129600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>80700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>69200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>80400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-133900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-166900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-171800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-206000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-205700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-322400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-251300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-186400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-54700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-159700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-306600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-123400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>34800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-85600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1616600</v>
+      </c>
+      <c r="E35" s="3">
         <v>102900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>129600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>80700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>69200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>80400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-133900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-166900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-171800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-206000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-205700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-322400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-251300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-186400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-54700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-159700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-306600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-123400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>34800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-85600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,83 +3438,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1630000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1723400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1527900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1428800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1354500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1351100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1046200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1013100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1272800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1036700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1079300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>892000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>972500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1440300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1530100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1255200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2261900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2567400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1439500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1466600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1623700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>520700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>684400</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3444,53 +3531,56 @@
       <c r="AF41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E42" s="3">
         <v>45600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>36600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>39000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>39400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>848600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>69700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>582700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>685400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>86500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>145500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3536,83 +3626,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>284400</v>
+      </c>
+      <c r="E43" s="3">
         <v>230700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>268200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>283700</v>
       </c>
-      <c r="G43" s="3">
-        <v>429900</v>
-      </c>
       <c r="H43" s="3">
+        <v>426200</v>
+      </c>
+      <c r="I43" s="3">
         <v>231900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>216800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>325000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>371300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>312700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>307300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>236200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>216300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>135800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>201600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>147800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>142100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>124600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>134600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>101000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>91600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>66100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>67000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>49000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3672,8 +3768,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3764,33 +3863,33 @@
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" s="3">
         <v>14300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>35200</v>
       </c>
       <c r="T45" s="3">
         <v>35200</v>
       </c>
       <c r="U45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="V45" s="3">
         <v>37300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>111300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>90900</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3806,59 +3905,62 @@
       <c r="AD45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2844000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2829000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2485900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2508200</v>
       </c>
-      <c r="G46" s="3">
-        <v>2297600</v>
-      </c>
       <c r="H46" s="3">
+        <v>2291700</v>
+      </c>
+      <c r="I46" s="3">
         <v>2053900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2049900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2613400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1786600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2567000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2543900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1866400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1623500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1692800</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3904,83 +4006,86 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9942500</v>
+      </c>
+      <c r="E47" s="3">
         <v>8815500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9022700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7613300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7503900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7073000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7131300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6249700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6513100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5465600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5290900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5304400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5369600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4605300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4453200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3826600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4003900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3008600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2790300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2585000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1958400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2099100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1757700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1290300</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,83 +4101,86 @@
       <c r="AF47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>708800</v>
+      </c>
+      <c r="E48" s="3">
         <v>691800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>665800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>630700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>591800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>564800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>523800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>492700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>449500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>425600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>394900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>366000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>320300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>311200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>292600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>256200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>222200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>194000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>169400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>143500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>120300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>113100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>49400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>49600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4088,77 +4196,80 @@
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>550900</v>
+      </c>
+      <c r="E49" s="3">
         <v>556700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>546100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>542600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>547100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>534800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>533900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>550200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>546900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>551100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>558600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>556200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>577000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>585400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>591400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>596000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>618500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>608300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>607600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>612100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>584400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>279200</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4174,14 +4285,17 @@
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,83 +4481,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E52" s="3">
         <v>241100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>226900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>171800</v>
       </c>
-      <c r="G52" s="3">
-        <v>200600</v>
-      </c>
       <c r="H52" s="3">
+        <v>206500</v>
+      </c>
+      <c r="I52" s="3">
         <v>194500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>224300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>212900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>202200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>171000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>254000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>314200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>242000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>313100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>459100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>422300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>335800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>440500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>298700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>256000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>260200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>216800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>137500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>112200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,83 +4671,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15790100</v>
+      </c>
+      <c r="E54" s="3">
         <v>13141600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12956900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11478600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11154900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10436200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10481100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10139200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9519600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9201400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9065000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8407100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8155600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7507800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7804800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7165100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6973800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7031700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6952400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5402100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4867000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4766400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2708100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2250500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,83 +4838,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E57" s="3">
         <v>59600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>82800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>50600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>57600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>59800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>30000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>425900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>29000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>26200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>24500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4800,44 +4931,47 @@
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12300</v>
       </c>
-      <c r="G58" s="3">
-        <v>16600</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>4200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>4100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4906,69 +5043,69 @@
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>53300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>249700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>220900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>211100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>151400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>213200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>180000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>200800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>177700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>80800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>49200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4984,53 +5121,56 @@
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>237500</v>
+      </c>
+      <c r="E60" s="3">
         <v>208900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>179500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>171700</v>
       </c>
-      <c r="G60" s="3">
-        <v>199500</v>
-      </c>
       <c r="H60" s="3">
+        <v>180100</v>
+      </c>
+      <c r="I60" s="3">
         <v>152400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>166800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>156400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>142600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>168900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>146100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>83800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5076,83 +5216,86 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10017300</v>
+      </c>
+      <c r="E61" s="3">
         <v>9087000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9173700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7946000</v>
       </c>
-      <c r="G61" s="3">
-        <v>7836700</v>
-      </c>
       <c r="H61" s="3">
+        <v>7853300</v>
+      </c>
+      <c r="I61" s="3">
         <v>7354100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7487600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7107300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6614300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6408700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6233200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5682200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5451000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4816500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4905700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4221200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4006800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4054400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3927900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2106500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1857300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2001500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1623400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1197800</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5168,53 +5311,56 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E62" s="3">
         <v>62300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62100</v>
       </c>
-      <c r="G62" s="3">
-        <v>49700</v>
-      </c>
       <c r="H62" s="3">
+        <v>52500</v>
+      </c>
+      <c r="I62" s="3">
         <v>54800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>69100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>96400</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,83 +5691,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10306300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9358200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9410000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8179700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8085900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7561300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7695500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7303600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6787600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6578000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6430100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5840300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5621400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4996700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5294600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4601600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4355500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4455700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4484100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3024700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2285800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2362400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1730400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1271500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5915,14 +6083,14 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>1327300</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1327200</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6201,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1127000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2743600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2846500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2976100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3056800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3126100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3128900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3209200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-888400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-734900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-494000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-462400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,83 +6581,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5483800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3783400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3546900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3298900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3069000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2874900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2785500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2835600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2732000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2623500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2634900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2566800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2534200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2511100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2510100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2563400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2618300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2576100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2468300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2377400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2581200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2404000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-349600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-348100</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>5</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1616600</v>
+      </c>
+      <c r="E81" s="3">
         <v>102900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>129600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>80700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>69200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>80400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-133900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-166900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-171800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-206000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-205700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-322400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-251300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-186400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-54700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-159700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-306600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-123400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-287100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>34800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-85600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,83 +7003,84 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E83" s="3">
         <v>59400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3700</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,83 +7571,86 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E89" s="3">
         <v>386500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>173700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>374600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>210400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>312000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>196900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>208200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>74300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-28500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-59100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-28000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-440300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>365200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-19900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-123300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-47700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,83 +7703,84 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-61400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-54400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-53000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-35800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-52500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-21800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,83 +7986,86 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1198300</v>
+      </c>
+      <c r="E94" s="3">
         <v>149400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1365000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-139600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-454500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>35500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-89100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-575000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-537600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-146800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-624900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-777200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-301000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-692200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>117300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-166000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-190100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-629500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>84300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-199700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-548900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-357800</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>5</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7929,8 +8163,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,83 +8496,86 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>865600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-152600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1186600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>110100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>387300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-245600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>144100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>465600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>146000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>112000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>506300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>148800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>609500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>669800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>199500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-28900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>55800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1766300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>244000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-176100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1488600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>447500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>817800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>5</v>
       </c>
@@ -8345,74 +8591,77 @@
       <c r="AF100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2700</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>5</v>
       </c>
@@ -8425,8 +8674,8 @@
       <c r="AB101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8437,83 +8686,86 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E102" s="3">
         <v>379700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>341200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>352500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>89200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-324300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>171700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>228500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-121500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-483300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-48700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>362700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-139200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1139000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-114400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1170200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-149100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>457700</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>5</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>5</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
